--- a/feedback_forms/049_visibility_and_coverage_survey--feedback_forms.xlsx
+++ b/feedback_forms/049_visibility_and_coverage_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'not_visible'}</t>
+          <t>not_visible</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Not visible'}</t>
+          <t>Not visible</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_visible'}</t>
+          <t>somewhat_visible</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Somewhat visible'}</t>
+          <t>Somewhat visible</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'highly_visible'}</t>
+          <t>highly_visible</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Highly visible'}</t>
+          <t>Highly visible</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'not_covered'}</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Not covered'}</t>
+          <t>Not covered</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_covered'}</t>
+          <t>somewhat_covered</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Somewhat covered'}</t>
+          <t>Somewhat covered</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'highly_covered'}</t>
+          <t>highly_covered</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Highly covered'}</t>
+          <t>Highly covered</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'very_highly_covered'}</t>
+          <t>very_highly_covered</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Very highly covered'}</t>
+          <t>Very highly covered</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'extremely_highly_covered'}</t>
+          <t>extremely_highly_covered</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Extremely highly covered'}</t>
+          <t>Extremely highly covered</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'completely_covered'}</t>
+          <t>completely_covered</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Completely covered'}</t>
+          <t>Completely covered</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Not likely'}</t>
+          <t>Not likely</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Somewhat likely'}</t>
+          <t>Somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'highly_likely'}</t>
+          <t>highly_likely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Highly likely'}</t>
+          <t>Highly likely</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Very likely'}</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'extremely_likely'}</t>
+          <t>extremely_likely</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Extremely likely'}</t>
+          <t>Extremely likely</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Not likely'}</t>
+          <t>Not likely</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Somewhat likely'}</t>
+          <t>Somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'highly_likely'}</t>
+          <t>highly_likely</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Highly likely'}</t>
+          <t>Highly likely</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Very likely'}</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'extremely_likely'}</t>
+          <t>extremely_likely</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Extremely likely'}</t>
+          <t>Extremely likely</t>
         </is>
       </c>
     </row>
